--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.63752117837744</v>
+        <v>9.203597191486335</v>
       </c>
       <c r="D2" t="n">
-        <v>27.02498475003614</v>
+        <v>4.391560021880873</v>
       </c>
       <c r="E2" t="n">
-        <v>19.24288691677158</v>
+        <v>3.126969123975381</v>
       </c>
       <c r="F2" t="n">
-        <v>6.940062845542887</v>
+        <v>1.127760212400719</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.57736343643437</v>
+        <v>6.431321558420586</v>
       </c>
       <c r="D3" t="n">
-        <v>12.98659645681419</v>
+        <v>2.110321924232307</v>
       </c>
       <c r="E3" t="n">
-        <v>19.24288691677158</v>
+        <v>3.126969123975381</v>
       </c>
       <c r="F3" t="n">
-        <v>6.940062845542887</v>
+        <v>1.127760212400719</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.63743533919971</v>
+        <v>4.978583242619953</v>
       </c>
       <c r="D4" t="n">
-        <v>8.841795289438164</v>
+        <v>1.436791734533702</v>
       </c>
       <c r="E4" t="n">
-        <v>19.24288691677158</v>
+        <v>3.126969123975381</v>
       </c>
       <c r="F4" t="n">
-        <v>6.940062845542887</v>
+        <v>1.127760212400719</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.57028428806599</v>
+        <v>9.680171196810724</v>
       </c>
       <c r="D5" t="n">
-        <v>11.07552789376232</v>
+        <v>1.799773282736377</v>
       </c>
       <c r="E5" t="n">
-        <v>19.24288691677158</v>
+        <v>3.126969123975381</v>
       </c>
       <c r="F5" t="n">
-        <v>6.940062845542887</v>
+        <v>1.127760212400719</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.2645112040992</v>
+        <v>3.45548307066612</v>
       </c>
       <c r="D6" t="n">
-        <v>25.40177159176108</v>
+        <v>4.127787883661175</v>
       </c>
       <c r="E6" t="n">
-        <v>19.24288691677158</v>
+        <v>3.126969123975381</v>
       </c>
       <c r="F6" t="n">
-        <v>6.940062845542887</v>
+        <v>1.127760212400719</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>78.4409613413215</v>
+        <v>12.74665621796474</v>
       </c>
       <c r="D7" t="n">
-        <v>16.63411274494624</v>
+        <v>2.703043321053764</v>
       </c>
       <c r="E7" t="n">
-        <v>19.24288691677158</v>
+        <v>3.126969123975381</v>
       </c>
       <c r="F7" t="n">
-        <v>6.940062845542887</v>
+        <v>1.127760212400719</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
